--- a/Supplemental_data/Supplemental data 11.xlsx
+++ b/Supplemental_data/Supplemental data 11.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="326">
   <si>
-    <t>GO terms enriched in DEDMGs in regions and contexts of ecotypes</t>
+    <t>GO enrichment in differentially expressed differentially methylated genes.</t>
   </si>
   <si>
     <t>Sheet name</t>
